--- a/backend/downloads/reports/Report_CA2301_2026.xlsx
+++ b/backend/downloads/reports/Report_CA2301_2026.xlsx
@@ -108,10 +108,10 @@
     <t>DIRECTPOATTAINMENT</t>
   </si>
   <si>
-    <t>{"CO1":{"grandTotal":1,"PO1":2,"PO2":2,"PO3":1,"PO4":"","PO5":2,"PO6":"","PO7":1,"PO8":3},"CO2":{"grandTotal":0.5,"PO1":2,"PO2":3,"PO3":2,"PO4":1,"PO5":"","PO6":2,"PO7":"","PO8":1},"CO3":{"grandTotal":0.8,"PO1":1,"PO2":1,"PO3":3,"PO4":2,"PO5":3,"PO6":"","PO7":2,"PO8":""},"CO4":{"grandTotal":1.5,"PO1":3,"PO2":2,"PO3":"","PO4":3,"PO5":1,"PO6":2,"PO7":3,"PO8":2},"CO5":{"grandTotal":2,"PO1":2,"PO2":"","PO3":2,"PO4":1,"PO5":2,"PO6":3,"PO7":1,"PO8":""}}</t>
-  </si>
-  <si>
-    <t>{"PO1":1.23,"PO2":0.91,"PO3":1.05,"PO4":1.23,"PO5":1.24,"PO6":1.43,"PO7":1.3,"PO8":1.08}</t>
+    <t>{"CO1":{"grandTotal":1,"PO1":2,"PO2":2,"PO3":1,"PO4":1,"PO5":2,"PO6":"","PO7":1,"PO8":3},"CO2":{"grandTotal":0.5,"PO1":2,"PO2":3,"PO3":2,"PO4":1,"PO5":"","PO6":2,"PO7":"","PO8":1},"CO3":{"grandTotal":0.8,"PO1":1,"PO2":1,"PO3":3,"PO4":2,"PO5":3,"PO6":"","PO7":2,"PO8":""},"CO4":{"grandTotal":1.5,"PO1":3,"PO2":2,"PO3":"","PO4":3,"PO5":1,"PO6":2,"PO7":3,"PO8":2},"CO5":{"grandTotal":2,"PO1":2,"PO2":"","PO3":2,"PO4":1,"PO5":2,"PO6":3,"PO7":1,"PO8":""}}</t>
+  </si>
+  <si>
+    <t>{"PO1":1.23,"PO2":0.91,"PO3":1.05,"PO4":1.2,"PO5":1.24,"PO6":1.43,"PO7":1.3,"PO8":1.08}</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1652,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="4">
-        <v>46169.27480583334</v>
+        <v>46179.71537337963</v>
       </c>
       <c r="C2">
         <v>1.16</v>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>46169.27570399306</v>
+        <v>46179.715983622686</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>

--- a/backend/downloads/reports/Report_CA2301_2026.xlsx
+++ b/backend/downloads/reports/Report_CA2301_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="42">
   <si>
     <t>Reg No</t>
   </si>
@@ -87,31 +87,58 @@
     <t>Attainment Level</t>
   </si>
   <si>
-    <t>Attainment Table</t>
-  </si>
-  <si>
-    <t>Calculated At</t>
+    <t>CO's</t>
+  </si>
+  <si>
+    <t>Sessional 1</t>
+  </si>
+  <si>
+    <t>Sessional 2</t>
+  </si>
+  <si>
+    <t>Total Avg Int</t>
+  </si>
+  <si>
+    <t>Grand Total (50% int + 50% End term)</t>
+  </si>
+  <si>
+    <t>Final CO Attainment</t>
+  </si>
+  <si>
+    <t>PO1</t>
+  </si>
+  <si>
+    <t>PO2</t>
+  </si>
+  <si>
+    <t>PO3</t>
+  </si>
+  <si>
+    <t>PO4</t>
+  </si>
+  <si>
+    <t>PO5</t>
+  </si>
+  <si>
+    <t>PO6</t>
+  </si>
+  <si>
+    <t>PO7</t>
+  </si>
+  <si>
+    <t>PO8</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
   <si>
     <t>Final Subject Attainment</t>
   </si>
   <si>
-    <t>{"CO1":{"Quiz_1":1,"Mid_Term":0,"Quiz_2":0,"Surprise_Quiz":1,"Assignment":3,"internalAvg":1,"externalLevel":1,"grandTotal":1},"CO2":{"Quiz_1":1,"Mid_Term":0,"Quiz_2":1,"Surprise_Quiz":1,"Assignment":2,"internalAvg":1,"externalLevel":0,"grandTotal":0.5},"CO3":{"Quiz_1":1,"Mid_Term":2,"Quiz_2":1,"Surprise_Quiz":1,"Assignment":3,"internalAvg":1.6,"externalLevel":0,"grandTotal":0.8},"CO4":{"Assignment":3,"internalAvg":3,"externalLevel":0,"grandTotal":1.5},"CO5":{"Assignment":3,"internalAvg":3,"externalLevel":1,"grandTotal":2}}</t>
-  </si>
-  <si>
-    <t>CALCULATEDAT</t>
-  </si>
-  <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>DIRECTPOATTAINMENT</t>
-  </si>
-  <si>
-    <t>{"CO1":{"grandTotal":1,"PO1":2,"PO2":2,"PO3":1,"PO4":1,"PO5":2,"PO6":"","PO7":1,"PO8":3},"CO2":{"grandTotal":0.5,"PO1":2,"PO2":3,"PO3":2,"PO4":1,"PO5":"","PO6":2,"PO7":"","PO8":1},"CO3":{"grandTotal":0.8,"PO1":1,"PO2":1,"PO3":3,"PO4":2,"PO5":3,"PO6":"","PO7":2,"PO8":""},"CO4":{"grandTotal":1.5,"PO1":3,"PO2":2,"PO3":"","PO4":3,"PO5":1,"PO6":2,"PO7":3,"PO8":2},"CO5":{"grandTotal":2,"PO1":2,"PO2":"","PO3":2,"PO4":1,"PO5":2,"PO6":3,"PO7":1,"PO8":""}}</t>
-  </si>
-  <si>
-    <t>{"PO1":1.23,"PO2":0.91,"PO3":1.05,"PO4":1.2,"PO5":1.24,"PO6":1.43,"PO7":1.3,"PO8":1.08}</t>
+    <t>Final PO Attainment</t>
   </si>
 </sst>
 </file>
@@ -130,15 +157,40 @@
       <b/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAEAEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0E0E0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -146,20 +198,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -503,7 +616,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -547,90 +660,90 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1630,35 +1743,193 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="4">
-        <v>46179.71537337963</v>
-      </c>
-      <c r="C2">
-        <v>1.16</v>
-      </c>
+      <c r="I1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>3</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
+        <v>3</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>3</v>
+      </c>
+      <c r="I6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:H7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1666,35 +1937,264 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="15" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>46179.715983622686</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D1" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>3</v>
+      </c>
+      <c r="I5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="6">
+        <v>2</v>
+      </c>
+      <c r="C7" s="6">
+        <v>2</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.6</v>
+      </c>
+      <c r="F7" s="6">
+        <v>2</v>
+      </c>
+      <c r="G7" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1.75</v>
+      </c>
+      <c r="I7" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="7">
+        <v>1.16</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.62</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.77</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.68</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0.77</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B8:I8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/backend/downloads/reports/Report_CA2301_2026.xlsx
+++ b/backend/downloads/reports/Report_CA2301_2026.xlsx
@@ -1924,7 +1924,9 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="5">
+        <v>1.16</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
